--- a/diseases/d190/2010-2014.xlsx
+++ b/diseases/d190/2010-2014.xlsx
@@ -769,11 +769,11 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>0.00100766683563812</v>
+        <v>0.000994862955488926</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
@@ -917,11 +917,11 @@
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>0.002519167089095299</v>
+        <v>0.002487157388722315</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
@@ -1065,11 +1065,11 @@
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0.02216867038403863</v>
+        <v>0.02188698502075637</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
@@ -1213,11 +1213,11 @@
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.003023000506914359</v>
+        <v>0.002984588866466778</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
@@ -1361,11 +1361,11 @@
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.008496383641748644</v>
+        <v>0.008383942674505923</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
@@ -1509,11 +1509,11 @@
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.002498936365220189</v>
+        <v>0.002465865492501742</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
@@ -1657,11 +1657,11 @@
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.001999149092176152</v>
+        <v>0.001972692394001393</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
@@ -1805,11 +1805,11 @@
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.004498085457396341</v>
+        <v>0.004438557886503136</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
@@ -1953,11 +1953,11 @@
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0.0289876618365542</v>
+        <v>0.02860403971302021</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
@@ -2101,11 +2101,11 @@
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0.003498510911308265</v>
+        <v>0.003452211689502438</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
@@ -2249,11 +2249,11 @@
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>0.001499361819132114</v>
+        <v>0.001479519295501045</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
@@ -2397,11 +2397,11 @@
         <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>0.0004997872730440379</v>
+        <v>0.0004931730985003484</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
@@ -2545,11 +2545,11 @@
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>0.005497660003484417</v>
+        <v>0.005424904083503833</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
@@ -2693,11 +2693,11 @@
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>0.003498510911308265</v>
+        <v>0.003452211689502438</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
@@ -2841,11 +2841,11 @@
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>0.01099532000696883</v>
+        <v>0.01084980816700767</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">

--- a/diseases/d190/2010-2014.xlsx
+++ b/diseases/d190/2010-2014.xlsx
@@ -776,6 +776,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO2" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -924,6 +929,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO3" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1072,6 +1082,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO4" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1220,6 +1235,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO5" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1368,6 +1388,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO6" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1516,6 +1541,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO7" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1664,6 +1694,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO8" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1812,6 +1847,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO9" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1960,6 +2000,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO10" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2108,6 +2153,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO11" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2256,6 +2306,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO12" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2404,6 +2459,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO13" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2552,6 +2612,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO14" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2700,6 +2765,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO15" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2846,6 +2916,11 @@
       <c r="S16" t="inlineStr">
         <is>
           <t>ibge_computed</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">

--- a/diseases/d190/2010-2014.xlsx
+++ b/diseases/d190/2010-2014.xlsx
@@ -771,11 +771,6 @@
       <c r="R2" t="n">
         <v>0.000994862955488926</v>
       </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -788,23 +783,13 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr"/>
       <c r="AT2" t="n">
         <v>0</v>
       </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV2" t="inlineStr">
         <is>
           <t>sinan_datasus</t>
@@ -924,11 +909,6 @@
       <c r="R3" t="n">
         <v>0.002487157388722315</v>
       </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -941,23 +921,13 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr"/>
       <c r="AT3" t="n">
         <v>0</v>
       </c>
-      <c r="AU3" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV3" t="inlineStr">
         <is>
           <t>sinan_datasus</t>
@@ -1077,11 +1047,6 @@
       <c r="R4" t="n">
         <v>0.02188698502075637</v>
       </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1094,23 +1059,13 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr"/>
       <c r="AT4" t="n">
         <v>0</v>
       </c>
-      <c r="AU4" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV4" t="inlineStr">
         <is>
           <t>sinan_datasus</t>
@@ -1230,11 +1185,6 @@
       <c r="R5" t="n">
         <v>0.002984588866466778</v>
       </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1247,23 +1197,13 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr"/>
       <c r="AT5" t="n">
         <v>0</v>
       </c>
-      <c r="AU5" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV5" t="inlineStr">
         <is>
           <t>sinan_datasus</t>
@@ -1383,11 +1323,6 @@
       <c r="R6" t="n">
         <v>0.008383942674505923</v>
       </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1400,23 +1335,13 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr"/>
       <c r="AT6" t="n">
         <v>0</v>
       </c>
-      <c r="AU6" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV6" t="inlineStr">
         <is>
           <t>sinan_datasus</t>
@@ -1536,11 +1461,6 @@
       <c r="R7" t="n">
         <v>0.002465865492501742</v>
       </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1553,23 +1473,13 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr"/>
       <c r="AT7" t="n">
         <v>0</v>
       </c>
-      <c r="AU7" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV7" t="inlineStr">
         <is>
           <t>sinan_datasus</t>
@@ -1689,11 +1599,6 @@
       <c r="R8" t="n">
         <v>0.001972692394001393</v>
       </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1706,23 +1611,13 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr"/>
       <c r="AT8" t="n">
         <v>0</v>
       </c>
-      <c r="AU8" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV8" t="inlineStr">
         <is>
           <t>sinan_datasus</t>
@@ -1842,11 +1737,6 @@
       <c r="R9" t="n">
         <v>0.004438557886503136</v>
       </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1859,23 +1749,13 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr"/>
       <c r="AT9" t="n">
         <v>0</v>
       </c>
-      <c r="AU9" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV9" t="inlineStr">
         <is>
           <t>sinan_datasus</t>
@@ -1995,11 +1875,6 @@
       <c r="R10" t="n">
         <v>0.02860403971302021</v>
       </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2012,23 +1887,13 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR10" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr"/>
       <c r="AT10" t="n">
         <v>0</v>
       </c>
-      <c r="AU10" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV10" t="inlineStr">
         <is>
           <t>sinan_datasus</t>
@@ -2148,11 +2013,6 @@
       <c r="R11" t="n">
         <v>0.003452211689502438</v>
       </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2165,23 +2025,13 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR11" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr"/>
       <c r="AT11" t="n">
         <v>0</v>
       </c>
-      <c r="AU11" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV11" t="inlineStr">
         <is>
           <t>sinan_datasus</t>
@@ -2301,11 +2151,6 @@
       <c r="R12" t="n">
         <v>0.001479519295501045</v>
       </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2318,23 +2163,13 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR12" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr"/>
       <c r="AT12" t="n">
         <v>0</v>
       </c>
-      <c r="AU12" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV12" t="inlineStr">
         <is>
           <t>sinan_datasus</t>
@@ -2454,11 +2289,6 @@
       <c r="R13" t="n">
         <v>0.0004931730985003484</v>
       </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2471,23 +2301,13 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR13" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr"/>
       <c r="AT13" t="n">
         <v>0</v>
       </c>
-      <c r="AU13" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV13" t="inlineStr">
         <is>
           <t>sinan_datasus</t>
@@ -2607,11 +2427,6 @@
       <c r="R14" t="n">
         <v>0.005424904083503833</v>
       </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2624,23 +2439,13 @@
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR14" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr"/>
       <c r="AT14" t="n">
         <v>0</v>
       </c>
-      <c r="AU14" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV14" t="inlineStr">
         <is>
           <t>sinan_datasus</t>
@@ -2760,11 +2565,6 @@
       <c r="R15" t="n">
         <v>0.003452211689502438</v>
       </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2777,23 +2577,13 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR15" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr"/>
       <c r="AT15" t="n">
         <v>0</v>
       </c>
-      <c r="AU15" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV15" t="inlineStr">
         <is>
           <t>sinan_datasus</t>
@@ -2913,11 +2703,6 @@
       <c r="R16" t="n">
         <v>0.01084980816700767</v>
       </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2930,22 +2715,12 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR16" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr"/>
       <c r="AT16" t="n">
         <v>0</v>
-      </c>
-      <c r="AU16" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>

--- a/diseases/d190/2010-2014.xlsx
+++ b/diseases/d190/2010-2014.xlsx
@@ -771,6 +771,11 @@
       <c r="R2" t="n">
         <v>0.000994862955488926</v>
       </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -783,13 +788,23 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr"/>
       <c r="AT2" t="n">
         <v>0</v>
       </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV2" t="inlineStr">
         <is>
           <t>sinan_datasus</t>
@@ -909,6 +924,11 @@
       <c r="R3" t="n">
         <v>0.002487157388722315</v>
       </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -921,13 +941,23 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr"/>
       <c r="AT3" t="n">
         <v>0</v>
       </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV3" t="inlineStr">
         <is>
           <t>sinan_datasus</t>
@@ -1047,6 +1077,11 @@
       <c r="R4" t="n">
         <v>0.02188698502075637</v>
       </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1059,13 +1094,23 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr"/>
       <c r="AT4" t="n">
         <v>0</v>
       </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV4" t="inlineStr">
         <is>
           <t>sinan_datasus</t>
@@ -1185,6 +1230,11 @@
       <c r="R5" t="n">
         <v>0.002984588866466778</v>
       </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1197,13 +1247,23 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr"/>
       <c r="AT5" t="n">
         <v>0</v>
       </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV5" t="inlineStr">
         <is>
           <t>sinan_datasus</t>
@@ -1323,6 +1383,11 @@
       <c r="R6" t="n">
         <v>0.008383942674505923</v>
       </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1335,13 +1400,23 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr"/>
       <c r="AT6" t="n">
         <v>0</v>
       </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV6" t="inlineStr">
         <is>
           <t>sinan_datasus</t>
@@ -1461,6 +1536,11 @@
       <c r="R7" t="n">
         <v>0.002465865492501742</v>
       </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1473,13 +1553,23 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr"/>
       <c r="AT7" t="n">
         <v>0</v>
       </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV7" t="inlineStr">
         <is>
           <t>sinan_datasus</t>
@@ -1599,6 +1689,11 @@
       <c r="R8" t="n">
         <v>0.001972692394001393</v>
       </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1611,13 +1706,23 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr"/>
       <c r="AT8" t="n">
         <v>0</v>
       </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV8" t="inlineStr">
         <is>
           <t>sinan_datasus</t>
@@ -1737,6 +1842,11 @@
       <c r="R9" t="n">
         <v>0.004438557886503136</v>
       </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1749,13 +1859,23 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr"/>
       <c r="AT9" t="n">
         <v>0</v>
       </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV9" t="inlineStr">
         <is>
           <t>sinan_datasus</t>
@@ -1875,6 +1995,11 @@
       <c r="R10" t="n">
         <v>0.02860403971302021</v>
       </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1887,13 +2012,23 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr"/>
       <c r="AT10" t="n">
         <v>0</v>
       </c>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV10" t="inlineStr">
         <is>
           <t>sinan_datasus</t>
@@ -2013,6 +2148,11 @@
       <c r="R11" t="n">
         <v>0.003452211689502438</v>
       </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2025,13 +2165,23 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr"/>
       <c r="AT11" t="n">
         <v>0</v>
       </c>
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV11" t="inlineStr">
         <is>
           <t>sinan_datasus</t>
@@ -2151,6 +2301,11 @@
       <c r="R12" t="n">
         <v>0.001479519295501045</v>
       </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2163,13 +2318,23 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR12" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr"/>
       <c r="AT12" t="n">
         <v>0</v>
       </c>
+      <c r="AU12" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV12" t="inlineStr">
         <is>
           <t>sinan_datasus</t>
@@ -2289,6 +2454,11 @@
       <c r="R13" t="n">
         <v>0.0004931730985003484</v>
       </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2301,13 +2471,23 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR13" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr"/>
       <c r="AT13" t="n">
         <v>0</v>
       </c>
+      <c r="AU13" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV13" t="inlineStr">
         <is>
           <t>sinan_datasus</t>
@@ -2427,6 +2607,11 @@
       <c r="R14" t="n">
         <v>0.005424904083503833</v>
       </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2439,13 +2624,23 @@
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR14" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr"/>
       <c r="AT14" t="n">
         <v>0</v>
       </c>
+      <c r="AU14" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV14" t="inlineStr">
         <is>
           <t>sinan_datasus</t>
@@ -2565,6 +2760,11 @@
       <c r="R15" t="n">
         <v>0.003452211689502438</v>
       </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2577,13 +2777,23 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR15" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr"/>
       <c r="AT15" t="n">
         <v>0</v>
       </c>
+      <c r="AU15" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV15" t="inlineStr">
         <is>
           <t>sinan_datasus</t>
@@ -2703,6 +2913,11 @@
       <c r="R16" t="n">
         <v>0.01084980816700767</v>
       </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2715,12 +2930,22 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR16" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr"/>
       <c r="AT16" t="n">
         <v>0</v>
+      </c>
+      <c r="AU16" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
